--- a/設計計画エクセル/第3回小課題2_分散分析_出席番号氏名.xlsx
+++ b/設計計画エクセル/第3回小課題2_分散分析_出席番号氏名.xlsx
@@ -35,11 +35,11 @@
     </font>
     <font>
       <name val="游ゴシック"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="游ゴシック"/>
-      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -82,34 +82,34 @@
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -496,25 +496,32 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>◆元データ（表3.1.1 グループにおける食事形態とキッチン面積の差）</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="36" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>被験者No.</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>自炊型
 (㎡)</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>コンビニ型
 (㎡)</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>外食型
 (㎡)</t>
@@ -522,313 +529,313 @@
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="5" t="n">
+      <c r="C4" s="6" t="n">
         <v>4.26</v>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>3.94</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>3.95</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="5" t="n">
+      <c r="C5" s="6" t="n">
         <v>7.24</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>5.31</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>2.45</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="5" t="n">
+      <c r="C6" s="6" t="n">
         <v>5.27</v>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>4.32</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>3.05</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="5" t="n">
+      <c r="C7" s="6" t="n">
         <v>6.25</v>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>4.33</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>3.52</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C8" s="6" t="n">
         <v>4.26</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>3.31</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>4.16</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="n">
+      <c r="C9" s="6" t="n">
         <v>6.12</v>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>3.05</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>3.18</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="5" t="n">
+      <c r="C10" s="6" t="n">
         <v>5.53</v>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>6.95</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>3.89</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="6" t="n">
         <v>6.34</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>5.58</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>3.37</v>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="6" t="n">
         <v>3.41</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>4.72</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="6" t="n">
         <v>3.69</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="C13" s="5" t="n">
+      <c r="C13" s="6" t="n">
         <v>5.74</v>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>4.28</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>4.05</v>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>標本平均</t>
         </is>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="8">
         <f>AVERAGE(C4:C13)</f>
         <v>5.442</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="8">
         <f>AVERAGE(D4:D13)</f>
         <v>4.579</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="8">
         <f>AVERAGE(E4:E13)</f>
         <v>3.531</v>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>標本数</t>
         </is>
       </c>
-      <c r="C16" s="8">
+      <c r="C16" s="9">
         <f>COUNT(C4:C13)</f>
         <v>10</v>
       </c>
-      <c r="D16" s="8">
+      <c r="D16" s="9">
         <f>COUNT(D4:D13)</f>
         <v>10</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="9">
         <f>COUNT(E4:E13)</f>
         <v>10</v>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>群内の変動（偏差平方和）</t>
         </is>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="8">
         <f>DEVSQ(C4:C13)</f>
         <v>12.20116</v>
       </c>
-      <c r="D17" s="7">
+      <c r="D17" s="8">
         <f>DEVSQ(D4:D13)</f>
         <v>11.75289</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="8">
         <f>DEVSQ(E4:E13)</f>
         <v>2.54389</v>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>（群平均－全体平均）²×標本数</t>
         </is>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="8">
         <f>C16*(C15-$C$20)^2</f>
         <v>8.55008444444443</v>
       </c>
-      <c r="D18" s="7">
+      <c r="D18" s="8">
         <f>D16*(D15-$C$20)^2</f>
         <v>0.0380277777777765</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="8">
         <f>E16*(E15-$C$20)^2</f>
         <v>9.72853444444446</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>全体の平均</t>
         </is>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="8">
         <f>AVERAGE(C4:E13)</f>
         <v>4.51733333333333</v>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>グループ数</t>
         </is>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="9">
         <f>COUNT(C15:E15)</f>
         <v>3</v>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>全体の標本数</t>
         </is>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="9">
         <f>COUNT(C4:E13)</f>
         <v>30</v>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="9" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>(1) ◆分散分析表</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>変動要因</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>変動</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>自由度</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>分散（不偏分散）</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Fの値</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>P値</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>確率95%のF</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>グループ間</t>
         </is>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="8">
         <f>SUM(C18:E18)</f>
         <v>18.3166466666667</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="9">
         <f>C21-1</f>
         <v>2</v>
       </c>
-      <c r="E26" s="7">
+      <c r="E26" s="8">
         <f>C26/D26</f>
         <v>9.15832333333333</v>
       </c>
@@ -846,48 +853,48 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>グループ内</t>
         </is>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="8">
         <f>SUM(C17:E17)</f>
         <v>26.49794</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="9">
         <f>C22-C21</f>
         <v>27</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E27" s="8">
         <f>C27/D27</f>
         <v>0.981405185185185</v>
       </c>
-      <c r="F27" s="7" t="n"/>
+      <c r="F27" s="8" t="n"/>
       <c r="G27" s="11" t="n"/>
-      <c r="H27" s="7" t="n"/>
+      <c r="H27" s="8" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>合計</t>
         </is>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="8">
         <f>C26+C27</f>
         <v>44.8145866666667</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="9">
         <f>D26+D27</f>
         <v>29</v>
       </c>
-      <c r="E28" s="7" t="n"/>
-      <c r="F28" s="7" t="n"/>
+      <c r="E28" s="8" t="n"/>
+      <c r="F28" s="8" t="n"/>
       <c r="G28" s="11" t="n"/>
-      <c r="H28" s="7" t="n"/>
+      <c r="H28" s="8" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -898,25 +905,25 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>（参考）合計の変動の確認</t>
         </is>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="8">
         <f>DEVSQ(C4:E13)</f>
         <v>44.8145866666667</v>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="9" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>◆解答</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="9" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
@@ -927,7 +934,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="9" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
